--- a/jogos_2025-06-25.xlsx
+++ b/jogos_2025-06-25.xlsx
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.73</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['26', '70', '9005']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['9002']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45833.35763888889</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.53</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['26', '70', '9005']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9002']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45833.35763888889</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2346,80 +2346,80 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['4', '79']</t>
+          <t>['40', '77', '86']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ15" t="n">
         <v>2.1</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,80 +2475,80 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['40', '77', '86']</t>
+          <t>['4', '79']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
         <v>2.1</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.13</v>
+        <v>3.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['23', '32', '42']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45833.85416666666</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.85</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.42</v>
+        <v>3.91</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>3.98</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['23', '32', '42']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['15', '49']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['45+2', '51', '58']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45833.85416666666</v>
@@ -2836,19 +2836,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="O19" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.63</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.17</v>
-      </c>
       <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['45', '65', '83']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45833.85416666666</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.56</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['15', '49']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['45', '65', '83']</t>
+          <t>['45+2', '51', '58']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3223,16 +3223,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>4.08</v>
+        <v>3.64</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>2.43</v>
       </c>
       <c r="O22" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" t="n">
         <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3', '90+6']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.39</v>
+        <v>2.78</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
@@ -3402,10 +3402,10 @@
         <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
         <v>1.04</v>
@@ -3417,44 +3417,44 @@
         <v>4.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['9003', '9006']</t>
+          <t>['40', '4503']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['7', '9', '22', '82']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45833.89583333334</v>
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="O24" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['30', '68']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['50', '57', '76', '90+9']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45833.89583333334</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X25" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['60', '63', '70']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['9004']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['40', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['7', '9', '22', '82']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45833.89583333334</v>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['30', '68']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['50', '57', '76', '90+9']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.25</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['60', '63', '70']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
